--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B03_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B03_Normal_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J220"/>
+  <dimension ref="A1:K220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -514,7 +519,10 @@
           <t>Ostium</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -551,6 +559,9 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>34.19156206107118</v>
       </c>
     </row>
@@ -589,6 +600,9 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>13.70480619480816</v>
       </c>
     </row>
@@ -627,6 +641,9 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>13.70480619480816</v>
       </c>
     </row>
@@ -665,6 +682,9 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>10.07391314257579</v>
       </c>
     </row>
@@ -703,6 +723,9 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>9.086312375561954</v>
       </c>
     </row>
@@ -741,6 +764,9 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>8.746824124790566</v>
       </c>
     </row>
@@ -779,6 +805,9 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>8.218179902291242</v>
       </c>
     </row>
@@ -817,6 +846,9 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>7.836770619901664</v>
       </c>
     </row>
@@ -855,6 +887,9 @@
         </is>
       </c>
       <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>7.162722102583384</v>
       </c>
     </row>
@@ -893,6 +928,9 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>7.310981061882006</v>
       </c>
     </row>
@@ -931,6 +969,9 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>7.037492341720552</v>
       </c>
     </row>
@@ -969,6 +1010,9 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>7.037492341720552</v>
       </c>
     </row>
@@ -1007,6 +1051,9 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
         <v>6.860158236481039</v>
       </c>
     </row>
@@ -1045,6 +1092,9 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>6.860158236481039</v>
       </c>
     </row>
@@ -1083,6 +1133,9 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>6.860158236481039</v>
       </c>
     </row>
@@ -1121,6 +1174,9 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>6.462664551863797</v>
       </c>
     </row>
@@ -1159,6 +1215,9 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>6.336005311670497</v>
       </c>
     </row>
@@ -1197,6 +1256,9 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>6.336005311670497</v>
       </c>
     </row>
@@ -1235,6 +1297,9 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>6.336005311670497</v>
       </c>
     </row>
@@ -1273,6 +1338,9 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>6.667695648258961</v>
       </c>
     </row>
@@ -1311,6 +1379,9 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>8.729501710970144</v>
       </c>
     </row>
@@ -1349,6 +1420,9 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
         <v>9.435939359634485</v>
       </c>
     </row>
@@ -1387,6 +1461,9 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>11.15912001892901</v>
       </c>
     </row>
@@ -1425,6 +1502,9 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>19</v>
+      </c>
+      <c r="K26" t="n">
         <v>1.227287714443503</v>
       </c>
     </row>
@@ -1463,6 +1543,9 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>19</v>
+      </c>
+      <c r="K27" t="n">
         <v>1.23193593309144</v>
       </c>
     </row>
@@ -1501,6 +1584,9 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>19</v>
+      </c>
+      <c r="K28" t="n">
         <v>1.35533946875624</v>
       </c>
     </row>
@@ -1539,6 +1625,9 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>19</v>
+      </c>
+      <c r="K29" t="n">
         <v>1.35533946875624</v>
       </c>
     </row>
@@ -1577,6 +1666,9 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>19</v>
+      </c>
+      <c r="K30" t="n">
         <v>1.377032682735515</v>
       </c>
     </row>
@@ -1615,6 +1707,9 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>19</v>
+      </c>
+      <c r="K31" t="n">
         <v>1.361532670712998</v>
       </c>
     </row>
@@ -1653,6 +1748,9 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>19</v>
+      </c>
+      <c r="K32" t="n">
         <v>1.361532670712998</v>
       </c>
     </row>
@@ -1691,6 +1789,9 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K33" t="n">
         <v>1.361532670712998</v>
       </c>
     </row>
@@ -1729,6 +1830,9 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>19</v>
+      </c>
+      <c r="K34" t="n">
         <v>1.361532670712998</v>
       </c>
     </row>
@@ -1767,6 +1871,9 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>19</v>
+      </c>
+      <c r="K35" t="n">
         <v>1.332550697377175</v>
       </c>
     </row>
@@ -1805,6 +1912,9 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>19</v>
+      </c>
+      <c r="K36" t="n">
         <v>1.332550697377175</v>
       </c>
     </row>
@@ -1843,6 +1953,9 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>19</v>
+      </c>
+      <c r="K37" t="n">
         <v>1.284651506328684</v>
       </c>
     </row>
@@ -1881,6 +1994,9 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" t="n">
         <v>1.107254980884808</v>
       </c>
     </row>
@@ -1919,6 +2035,9 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" t="n">
         <v>1.112638311549703</v>
       </c>
     </row>
@@ -1957,6 +2076,9 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" t="n">
         <v>1.112638311549703</v>
       </c>
     </row>
@@ -1995,6 +2117,9 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>19</v>
+      </c>
+      <c r="K41" t="n">
         <v>1.257088550825828</v>
       </c>
     </row>
@@ -2033,6 +2158,9 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>19</v>
+      </c>
+      <c r="K42" t="n">
         <v>1.318599484561683</v>
       </c>
     </row>
@@ -2071,6 +2199,9 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>19</v>
+      </c>
+      <c r="K43" t="n">
         <v>1.318599484561683</v>
       </c>
     </row>
@@ -2109,6 +2240,9 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>19</v>
+      </c>
+      <c r="K44" t="n">
         <v>1.668579154133544</v>
       </c>
     </row>
@@ -2147,6 +2281,9 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>19</v>
+      </c>
+      <c r="K45" t="n">
         <v>2.154789540514063</v>
       </c>
     </row>
@@ -2185,6 +2322,9 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>19</v>
+      </c>
+      <c r="K46" t="n">
         <v>2.297674616284092</v>
       </c>
     </row>
@@ -2223,6 +2363,9 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>19</v>
+      </c>
+      <c r="K47" t="n">
         <v>2.458820606152787</v>
       </c>
     </row>
@@ -2261,6 +2404,9 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>19</v>
+      </c>
+      <c r="K48" t="n">
         <v>2.460406747861397</v>
       </c>
     </row>
@@ -2299,6 +2445,9 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>19</v>
+      </c>
+      <c r="K49" t="n">
         <v>2.410618974223967</v>
       </c>
     </row>
@@ -2337,6 +2486,9 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>19</v>
+      </c>
+      <c r="K50" t="n">
         <v>2.270371957171189</v>
       </c>
     </row>
@@ -2375,6 +2527,9 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>19</v>
+      </c>
+      <c r="K51" t="n">
         <v>2.271869422281108</v>
       </c>
     </row>
@@ -2413,6 +2568,9 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>19</v>
+      </c>
+      <c r="K52" t="n">
         <v>2.271869422281108</v>
       </c>
     </row>
@@ -2451,6 +2609,9 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>19</v>
+      </c>
+      <c r="K53" t="n">
         <v>2.216039524358943</v>
       </c>
     </row>
@@ -2489,6 +2650,9 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>19</v>
+      </c>
+      <c r="K54" t="n">
         <v>2.216039524358943</v>
       </c>
     </row>
@@ -2527,6 +2691,9 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>19</v>
+      </c>
+      <c r="K55" t="n">
         <v>2.213941658042832</v>
       </c>
     </row>
@@ -2565,6 +2732,9 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>19</v>
+      </c>
+      <c r="K56" t="n">
         <v>2.235270250419494</v>
       </c>
     </row>
@@ -2603,6 +2773,9 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>19</v>
+      </c>
+      <c r="K57" t="n">
         <v>2.274306125900985</v>
       </c>
     </row>
@@ -2641,6 +2814,9 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>19</v>
+      </c>
+      <c r="K58" t="n">
         <v>2.274306125900985</v>
       </c>
     </row>
@@ -2679,6 +2855,9 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>19</v>
+      </c>
+      <c r="K59" t="n">
         <v>2.260946222053909</v>
       </c>
     </row>
@@ -2717,6 +2896,9 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>19</v>
+      </c>
+      <c r="K60" t="n">
         <v>2.183887499719703</v>
       </c>
     </row>
@@ -2755,6 +2937,9 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>19</v>
+      </c>
+      <c r="K61" t="n">
         <v>1.970594865057129</v>
       </c>
     </row>
@@ -2793,6 +2978,9 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>19</v>
+      </c>
+      <c r="K62" t="n">
         <v>1.910386319788868</v>
       </c>
     </row>
@@ -2831,6 +3019,9 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>19</v>
+      </c>
+      <c r="K63" t="n">
         <v>1.810542151060285</v>
       </c>
     </row>
@@ -2869,6 +3060,9 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>19</v>
+      </c>
+      <c r="K64" t="n">
         <v>1.829812881081303</v>
       </c>
     </row>
@@ -2907,6 +3101,9 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>19</v>
+      </c>
+      <c r="K65" t="n">
         <v>1.829812881081303</v>
       </c>
     </row>
@@ -2945,6 +3142,9 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>19</v>
+      </c>
+      <c r="K66" t="n">
         <v>1.991065770279512</v>
       </c>
     </row>
@@ -2983,6 +3183,9 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>19</v>
+      </c>
+      <c r="K67" t="n">
         <v>1.991065770279512</v>
       </c>
     </row>
@@ -3021,6 +3224,9 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>19</v>
+      </c>
+      <c r="K68" t="n">
         <v>2.137351514017634</v>
       </c>
     </row>
@@ -3059,6 +3265,9 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>19</v>
+      </c>
+      <c r="K69" t="n">
         <v>2.221422323211839</v>
       </c>
     </row>
@@ -3097,6 +3306,9 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>19</v>
+      </c>
+      <c r="K70" t="n">
         <v>2.219204132671578</v>
       </c>
     </row>
@@ -3135,6 +3347,9 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>19</v>
+      </c>
+      <c r="K71" t="n">
         <v>2.215632077142135</v>
       </c>
     </row>
@@ -3173,6 +3388,9 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>19</v>
+      </c>
+      <c r="K72" t="n">
         <v>2.229827140497467</v>
       </c>
     </row>
@@ -3211,6 +3429,9 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>19</v>
+      </c>
+      <c r="K73" t="n">
         <v>2.229827140497467</v>
       </c>
     </row>
@@ -3249,6 +3470,9 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>19</v>
+      </c>
+      <c r="K74" t="n">
         <v>2.319870152035572</v>
       </c>
     </row>
@@ -3287,6 +3511,9 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>19</v>
+      </c>
+      <c r="K75" t="n">
         <v>2.40130937562907</v>
       </c>
     </row>
@@ -3325,6 +3552,9 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>19</v>
+      </c>
+      <c r="K76" t="n">
         <v>2.40130937562907</v>
       </c>
     </row>
@@ -3363,6 +3593,9 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>19</v>
+      </c>
+      <c r="K77" t="n">
         <v>2.537929763195659</v>
       </c>
     </row>
@@ -3401,6 +3634,9 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>19</v>
+      </c>
+      <c r="K78" t="n">
         <v>2.537929763195659</v>
       </c>
     </row>
@@ -3439,6 +3675,9 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>19</v>
+      </c>
+      <c r="K79" t="n">
         <v>2.568277899878588</v>
       </c>
     </row>
@@ -3477,6 +3716,9 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>19</v>
+      </c>
+      <c r="K80" t="n">
         <v>2.552397377840622</v>
       </c>
     </row>
@@ -3515,6 +3757,9 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>19</v>
+      </c>
+      <c r="K81" t="n">
         <v>2.552397377840622</v>
       </c>
     </row>
@@ -3553,6 +3798,9 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>19</v>
+      </c>
+      <c r="K82" t="n">
         <v>2.52490559672174</v>
       </c>
     </row>
@@ -3591,6 +3839,9 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>19</v>
+      </c>
+      <c r="K83" t="n">
         <v>2.458664129952975</v>
       </c>
     </row>
@@ -3629,6 +3880,9 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>19</v>
+      </c>
+      <c r="K84" t="n">
         <v>2.458664129952975</v>
       </c>
     </row>
@@ -3667,6 +3921,9 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>19</v>
+      </c>
+      <c r="K85" t="n">
         <v>2.340751823293324</v>
       </c>
     </row>
@@ -3705,6 +3962,9 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>19</v>
+      </c>
+      <c r="K86" t="n">
         <v>2.336561586544111</v>
       </c>
     </row>
@@ -3743,6 +4003,9 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>19</v>
+      </c>
+      <c r="K87" t="n">
         <v>2.328929626762258</v>
       </c>
     </row>
@@ -3781,6 +4044,9 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>19</v>
+      </c>
+      <c r="K88" t="n">
         <v>2.291460197292751</v>
       </c>
     </row>
@@ -3819,6 +4085,9 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>19</v>
+      </c>
+      <c r="K89" t="n">
         <v>2.291460197292751</v>
       </c>
     </row>
@@ -3857,6 +4126,9 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>19</v>
+      </c>
+      <c r="K90" t="n">
         <v>2.291460197292751</v>
       </c>
     </row>
@@ -3895,6 +4167,9 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>19</v>
+      </c>
+      <c r="K91" t="n">
         <v>2.256392889218995</v>
       </c>
     </row>
@@ -3933,6 +4208,9 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>19</v>
+      </c>
+      <c r="K92" t="n">
         <v>2.252810073838055</v>
       </c>
     </row>
@@ -3971,6 +4249,9 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>19</v>
+      </c>
+      <c r="K93" t="n">
         <v>2.252810073838055</v>
       </c>
     </row>
@@ -4009,6 +4290,9 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>19</v>
+      </c>
+      <c r="K94" t="n">
         <v>2.241589356169574</v>
       </c>
     </row>
@@ -4047,6 +4331,9 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>19</v>
+      </c>
+      <c r="K95" t="n">
         <v>2.256258194428659</v>
       </c>
     </row>
@@ -4085,6 +4372,9 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>19</v>
+      </c>
+      <c r="K96" t="n">
         <v>2.275320402532291</v>
       </c>
     </row>
@@ -4123,6 +4413,9 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>19</v>
+      </c>
+      <c r="K97" t="n">
         <v>2.275320402532291</v>
       </c>
     </row>
@@ -4161,6 +4454,9 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>19</v>
+      </c>
+      <c r="K98" t="n">
         <v>2.34160528784422</v>
       </c>
     </row>
@@ -4199,6 +4495,9 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>19</v>
+      </c>
+      <c r="K99" t="n">
         <v>2.34160528784422</v>
       </c>
     </row>
@@ -4237,6 +4536,9 @@
         </is>
       </c>
       <c r="J100" t="n">
+        <v>19</v>
+      </c>
+      <c r="K100" t="n">
         <v>2.530274206826251</v>
       </c>
     </row>
@@ -4275,6 +4577,9 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>19</v>
+      </c>
+      <c r="K101" t="n">
         <v>2.530274206826251</v>
       </c>
     </row>
@@ -4313,6 +4618,9 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>19</v>
+      </c>
+      <c r="K102" t="n">
         <v>2.584584463834299</v>
       </c>
     </row>
@@ -4351,6 +4659,9 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>19</v>
+      </c>
+      <c r="K103" t="n">
         <v>2.586206055763945</v>
       </c>
     </row>
@@ -4389,6 +4700,9 @@
         </is>
       </c>
       <c r="J104" t="n">
+        <v>19</v>
+      </c>
+      <c r="K104" t="n">
         <v>2.586206055763945</v>
       </c>
     </row>
@@ -4427,6 +4741,9 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>19</v>
+      </c>
+      <c r="K105" t="n">
         <v>2.586206055763945</v>
       </c>
     </row>
@@ -4465,6 +4782,9 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>19</v>
+      </c>
+      <c r="K106" t="n">
         <v>2.544664688156764</v>
       </c>
     </row>
@@ -4503,6 +4823,9 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>19</v>
+      </c>
+      <c r="K107" t="n">
         <v>2.529506928743095</v>
       </c>
     </row>
@@ -4541,6 +4864,9 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>19</v>
+      </c>
+      <c r="K108" t="n">
         <v>2.497336168150439</v>
       </c>
     </row>
@@ -4579,6 +4905,9 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>19</v>
+      </c>
+      <c r="K109" t="n">
         <v>2.446076643315274</v>
       </c>
     </row>
@@ -4617,6 +4946,9 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>19</v>
+      </c>
+      <c r="K110" t="n">
         <v>2.411004224014718</v>
       </c>
     </row>
@@ -4655,6 +4987,9 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>19</v>
+      </c>
+      <c r="K111" t="n">
         <v>2.401508938888195</v>
       </c>
     </row>
@@ -4693,6 +5028,9 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>19</v>
+      </c>
+      <c r="K112" t="n">
         <v>2.401508938888195</v>
       </c>
     </row>
@@ -4731,6 +5069,9 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>19</v>
+      </c>
+      <c r="K113" t="n">
         <v>2.355374210797699</v>
       </c>
     </row>
@@ -4769,6 +5110,9 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>19</v>
+      </c>
+      <c r="K114" t="n">
         <v>2.355374210797699</v>
       </c>
     </row>
@@ -4807,6 +5151,9 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>19</v>
+      </c>
+      <c r="K115" t="n">
         <v>2.315226465388985</v>
       </c>
     </row>
@@ -4845,6 +5192,9 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>19</v>
+      </c>
+      <c r="K116" t="n">
         <v>2.315226465388985</v>
       </c>
     </row>
@@ -4883,6 +5233,9 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>19</v>
+      </c>
+      <c r="K117" t="n">
         <v>2.457069773380443</v>
       </c>
     </row>
@@ -4921,6 +5274,9 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>19</v>
+      </c>
+      <c r="K118" t="n">
         <v>2.457069773380443</v>
       </c>
     </row>
@@ -4959,6 +5315,9 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>19</v>
+      </c>
+      <c r="K119" t="n">
         <v>2.482427983219213</v>
       </c>
     </row>
@@ -4997,6 +5356,9 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>19</v>
+      </c>
+      <c r="K120" t="n">
         <v>2.511628680011507</v>
       </c>
     </row>
@@ -5035,6 +5397,9 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>19</v>
+      </c>
+      <c r="K121" t="n">
         <v>2.552545134477885</v>
       </c>
     </row>
@@ -5073,6 +5438,9 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>19</v>
+      </c>
+      <c r="K122" t="n">
         <v>2.555830182603009</v>
       </c>
     </row>
@@ -5111,6 +5479,9 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>19</v>
+      </c>
+      <c r="K123" t="n">
         <v>2.549148888523415</v>
       </c>
     </row>
@@ -5149,6 +5520,9 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>19</v>
+      </c>
+      <c r="K124" t="n">
         <v>2.515759755719835</v>
       </c>
     </row>
@@ -5187,6 +5561,9 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>19</v>
+      </c>
+      <c r="K125" t="n">
         <v>2.528679156446047</v>
       </c>
     </row>
@@ -5225,6 +5602,9 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>19</v>
+      </c>
+      <c r="K126" t="n">
         <v>2.533869015876358</v>
       </c>
     </row>
@@ -5263,6 +5643,9 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>19</v>
+      </c>
+      <c r="K127" t="n">
         <v>2.530864023077452</v>
       </c>
     </row>
@@ -5301,6 +5684,9 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>19</v>
+      </c>
+      <c r="K128" t="n">
         <v>2.516545216993899</v>
       </c>
     </row>
@@ -5339,6 +5725,9 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>19</v>
+      </c>
+      <c r="K129" t="n">
         <v>2.516545216993899</v>
       </c>
     </row>
@@ -5377,6 +5766,9 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>19</v>
+      </c>
+      <c r="K130" t="n">
         <v>2.516545216993899</v>
       </c>
     </row>
@@ -5415,6 +5807,9 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>19</v>
+      </c>
+      <c r="K131" t="n">
         <v>2.523017728759505</v>
       </c>
     </row>
@@ -5453,6 +5848,9 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>19</v>
+      </c>
+      <c r="K132" t="n">
         <v>2.543958390346354</v>
       </c>
     </row>
@@ -5491,6 +5889,9 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>19</v>
+      </c>
+      <c r="K133" t="n">
         <v>2.543958390346354</v>
       </c>
     </row>
@@ -5529,6 +5930,9 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>19</v>
+      </c>
+      <c r="K134" t="n">
         <v>2.485677645008055</v>
       </c>
     </row>
@@ -5567,6 +5971,9 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>19</v>
+      </c>
+      <c r="K135" t="n">
         <v>2.485677645008055</v>
       </c>
     </row>
@@ -5605,6 +6012,9 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>19</v>
+      </c>
+      <c r="K136" t="n">
         <v>2.451207524165408</v>
       </c>
     </row>
@@ -5643,6 +6053,9 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>19</v>
+      </c>
+      <c r="K137" t="n">
         <v>2.402168259650153</v>
       </c>
     </row>
@@ -5681,6 +6094,9 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>19</v>
+      </c>
+      <c r="K138" t="n">
         <v>2.402168259650153</v>
       </c>
     </row>
@@ -5719,6 +6135,9 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>19</v>
+      </c>
+      <c r="K139" t="n">
         <v>2.190765346481614</v>
       </c>
     </row>
@@ -5757,6 +6176,9 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>19</v>
+      </c>
+      <c r="K140" t="n">
         <v>2.123036630767556</v>
       </c>
     </row>
@@ -5795,6 +6217,9 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>19</v>
+      </c>
+      <c r="K141" t="n">
         <v>2.019402621132054</v>
       </c>
     </row>
@@ -5833,6 +6258,9 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>19</v>
+      </c>
+      <c r="K142" t="n">
         <v>1.992580752593158</v>
       </c>
     </row>
@@ -5871,6 +6299,9 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>19</v>
+      </c>
+      <c r="K143" t="n">
         <v>1.992580752593158</v>
       </c>
     </row>
@@ -5909,6 +6340,9 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>19</v>
+      </c>
+      <c r="K144" t="n">
         <v>1.957100819987285</v>
       </c>
     </row>
@@ -5947,6 +6381,9 @@
         </is>
       </c>
       <c r="J145" t="n">
+        <v>19</v>
+      </c>
+      <c r="K145" t="n">
         <v>1.912286907795664</v>
       </c>
     </row>
@@ -5985,6 +6422,9 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>19</v>
+      </c>
+      <c r="K146" t="n">
         <v>1.880302071203517</v>
       </c>
     </row>
@@ -6023,6 +6463,9 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>19</v>
+      </c>
+      <c r="K147" t="n">
         <v>1.833191292616835</v>
       </c>
     </row>
@@ -6061,6 +6504,9 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>19</v>
+      </c>
+      <c r="K148" t="n">
         <v>1.835108269023008</v>
       </c>
     </row>
@@ -6099,6 +6545,9 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>19</v>
+      </c>
+      <c r="K149" t="n">
         <v>1.837290468265474</v>
       </c>
     </row>
@@ -6137,6 +6586,9 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>19</v>
+      </c>
+      <c r="K150" t="n">
         <v>1.851183425352798</v>
       </c>
     </row>
@@ -6175,6 +6627,9 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>19</v>
+      </c>
+      <c r="K151" t="n">
         <v>1.851183425352798</v>
       </c>
     </row>
@@ -6213,6 +6668,9 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>19</v>
+      </c>
+      <c r="K152" t="n">
         <v>1.851183425352798</v>
       </c>
     </row>
@@ -6251,6 +6709,9 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>19</v>
+      </c>
+      <c r="K153" t="n">
         <v>1.918307120376766</v>
       </c>
     </row>
@@ -6289,6 +6750,9 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>19</v>
+      </c>
+      <c r="K154" t="n">
         <v>1.985832791947801</v>
       </c>
     </row>
@@ -6327,6 +6791,9 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>19</v>
+      </c>
+      <c r="K155" t="n">
         <v>1.94111181613984</v>
       </c>
     </row>
@@ -6365,6 +6832,9 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>19</v>
+      </c>
+      <c r="K156" t="n">
         <v>1.884597235153793</v>
       </c>
     </row>
@@ -6403,6 +6873,9 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>19</v>
+      </c>
+      <c r="K157" t="n">
         <v>1.884597235153793</v>
       </c>
     </row>
@@ -6441,6 +6914,9 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>19</v>
+      </c>
+      <c r="K158" t="n">
         <v>1.884597235153793</v>
       </c>
     </row>
@@ -6479,6 +6955,9 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>19</v>
+      </c>
+      <c r="K159" t="n">
         <v>1.621958698060077</v>
       </c>
     </row>
@@ -6517,6 +6996,9 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>19</v>
+      </c>
+      <c r="K160" t="n">
         <v>1.621958698060077</v>
       </c>
     </row>
@@ -6555,6 +7037,9 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>19</v>
+      </c>
+      <c r="K161" t="n">
         <v>1.379798047976322</v>
       </c>
     </row>
@@ -6593,6 +7078,9 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>19</v>
+      </c>
+      <c r="K162" t="n">
         <v>1.333362209138855</v>
       </c>
     </row>
@@ -6631,6 +7119,9 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>19</v>
+      </c>
+      <c r="K163" t="n">
         <v>1.333362209138855</v>
       </c>
     </row>
@@ -6669,6 +7160,9 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>19</v>
+      </c>
+      <c r="K164" t="n">
         <v>1.287433504266253</v>
       </c>
     </row>
@@ -6707,6 +7201,9 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>19</v>
+      </c>
+      <c r="K165" t="n">
         <v>1.211808301441334</v>
       </c>
     </row>
@@ -6745,6 +7242,9 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>19</v>
+      </c>
+      <c r="K166" t="n">
         <v>1.205523507937499</v>
       </c>
     </row>
@@ -6783,6 +7283,9 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>19</v>
+      </c>
+      <c r="K167" t="n">
         <v>1.205523507937499</v>
       </c>
     </row>
@@ -6821,6 +7324,9 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>19</v>
+      </c>
+      <c r="K168" t="n">
         <v>1.205523507937499</v>
       </c>
     </row>
@@ -6859,6 +7365,9 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>19</v>
+      </c>
+      <c r="K169" t="n">
         <v>1.1928574441495</v>
       </c>
     </row>
@@ -6897,6 +7406,9 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>19</v>
+      </c>
+      <c r="K170" t="n">
         <v>1.16536180842725</v>
       </c>
     </row>
@@ -6935,6 +7447,9 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>19</v>
+      </c>
+      <c r="K171" t="n">
         <v>1.16536180842725</v>
       </c>
     </row>
@@ -6973,6 +7488,9 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>19</v>
+      </c>
+      <c r="K172" t="n">
         <v>1.236228494084955</v>
       </c>
     </row>
@@ -7011,6 +7529,9 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>19</v>
+      </c>
+      <c r="K173" t="n">
         <v>1.236228494084955</v>
       </c>
     </row>
@@ -7049,6 +7570,9 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>19</v>
+      </c>
+      <c r="K174" t="n">
         <v>1.260336599441735</v>
       </c>
     </row>
@@ -7087,6 +7611,9 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>19</v>
+      </c>
+      <c r="K175" t="n">
         <v>1.297429051340093</v>
       </c>
     </row>
@@ -7125,6 +7652,9 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>19</v>
+      </c>
+      <c r="K176" t="n">
         <v>1.297429051340093</v>
       </c>
     </row>
@@ -7163,6 +7693,9 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>19</v>
+      </c>
+      <c r="K177" t="n">
         <v>1.30326712508255</v>
       </c>
     </row>
@@ -7201,6 +7734,9 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>19</v>
+      </c>
+      <c r="K178" t="n">
         <v>1.281377167733944</v>
       </c>
     </row>
@@ -7239,6 +7775,9 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>19</v>
+      </c>
+      <c r="K179" t="n">
         <v>1.251783703030703</v>
       </c>
     </row>
@@ -7277,6 +7816,9 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>19</v>
+      </c>
+      <c r="K180" t="n">
         <v>1.227335525810869</v>
       </c>
     </row>
@@ -7315,6 +7857,9 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>19</v>
+      </c>
+      <c r="K181" t="n">
         <v>1.243950820717568</v>
       </c>
     </row>
@@ -7353,6 +7898,9 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>19</v>
+      </c>
+      <c r="K182" t="n">
         <v>1.243950820717568</v>
       </c>
     </row>
@@ -7391,6 +7939,9 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>19</v>
+      </c>
+      <c r="K183" t="n">
         <v>1.243950820717568</v>
       </c>
     </row>
@@ -7429,6 +7980,9 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>19</v>
+      </c>
+      <c r="K184" t="n">
         <v>1.289010081981549</v>
       </c>
     </row>
@@ -7467,6 +8021,9 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>19</v>
+      </c>
+      <c r="K185" t="n">
         <v>1.289010081981549</v>
       </c>
     </row>
@@ -7505,6 +8062,9 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>19</v>
+      </c>
+      <c r="K186" t="n">
         <v>1.30978613598686</v>
       </c>
     </row>
@@ -7543,6 +8103,9 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>19</v>
+      </c>
+      <c r="K187" t="n">
         <v>1.30978613598686</v>
       </c>
     </row>
@@ -7581,6 +8144,9 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>19</v>
+      </c>
+      <c r="K188" t="n">
         <v>1.353093274823836</v>
       </c>
     </row>
@@ -7619,6 +8185,9 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>19</v>
+      </c>
+      <c r="K189" t="n">
         <v>1.349097862080286</v>
       </c>
     </row>
@@ -7657,6 +8226,9 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>19</v>
+      </c>
+      <c r="K190" t="n">
         <v>1.349097862080286</v>
       </c>
     </row>
@@ -7695,6 +8267,9 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>19</v>
+      </c>
+      <c r="K191" t="n">
         <v>1.349097862080286</v>
       </c>
     </row>
@@ -7733,6 +8308,9 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>19</v>
+      </c>
+      <c r="K192" t="n">
         <v>1.249019127836197</v>
       </c>
     </row>
@@ -7771,6 +8349,9 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>19</v>
+      </c>
+      <c r="K193" t="n">
         <v>1.146242541840859</v>
       </c>
     </row>
@@ -7809,6 +8390,9 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>19</v>
+      </c>
+      <c r="K194" t="n">
         <v>1.071318962206051</v>
       </c>
     </row>
@@ -7847,6 +8431,9 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>19</v>
+      </c>
+      <c r="K195" t="n">
         <v>0.9282874515275316</v>
       </c>
     </row>
@@ -7885,6 +8472,9 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>19</v>
+      </c>
+      <c r="K196" t="n">
         <v>0.8844761571323866</v>
       </c>
     </row>
@@ -7923,6 +8513,9 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>19</v>
+      </c>
+      <c r="K197" t="n">
         <v>0.8922070873695911</v>
       </c>
     </row>
@@ -7961,6 +8554,9 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>19</v>
+      </c>
+      <c r="K198" t="n">
         <v>1.145696371936362</v>
       </c>
     </row>
@@ -7999,6 +8595,9 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>19</v>
+      </c>
+      <c r="K199" t="n">
         <v>1.210838832206954</v>
       </c>
     </row>
@@ -8037,6 +8636,9 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>19</v>
+      </c>
+      <c r="K200" t="n">
         <v>1.265759784093344</v>
       </c>
     </row>
@@ -8075,6 +8677,9 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>19</v>
+      </c>
+      <c r="K201" t="n">
         <v>1.265759784093344</v>
       </c>
     </row>
@@ -8113,6 +8718,9 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>19</v>
+      </c>
+      <c r="K202" t="n">
         <v>1.296048767498403</v>
       </c>
     </row>
@@ -8151,6 +8759,9 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>19</v>
+      </c>
+      <c r="K203" t="n">
         <v>1.298801741278553</v>
       </c>
     </row>
@@ -8189,6 +8800,9 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>19</v>
+      </c>
+      <c r="K204" t="n">
         <v>1.286869092677173</v>
       </c>
     </row>
@@ -8227,6 +8841,9 @@
         </is>
       </c>
       <c r="J205" t="n">
+        <v>19</v>
+      </c>
+      <c r="K205" t="n">
         <v>1.233372560532288</v>
       </c>
     </row>
@@ -8265,6 +8882,9 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>19</v>
+      </c>
+      <c r="K206" t="n">
         <v>1.233372560532288</v>
       </c>
     </row>
@@ -8303,6 +8923,9 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>19</v>
+      </c>
+      <c r="K207" t="n">
         <v>1.13176711732786</v>
       </c>
     </row>
@@ -8341,6 +8964,9 @@
         </is>
       </c>
       <c r="J208" t="n">
+        <v>19</v>
+      </c>
+      <c r="K208" t="n">
         <v>0.936908567612344</v>
       </c>
     </row>
@@ -8379,6 +9005,9 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>19</v>
+      </c>
+      <c r="K209" t="n">
         <v>0.8539973695115169</v>
       </c>
     </row>
@@ -8417,6 +9046,9 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>19</v>
+      </c>
+      <c r="K210" t="n">
         <v>0.822075033593868</v>
       </c>
     </row>
@@ -8455,6 +9087,9 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>19</v>
+      </c>
+      <c r="K211" t="n">
         <v>0.822075033593868</v>
       </c>
     </row>
@@ -8493,6 +9128,9 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>19</v>
+      </c>
+      <c r="K212" t="n">
         <v>0.7864108338360511</v>
       </c>
     </row>
@@ -8531,6 +9169,9 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>19</v>
+      </c>
+      <c r="K213" t="n">
         <v>0.7371944434193791</v>
       </c>
     </row>
@@ -8569,6 +9210,9 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>19</v>
+      </c>
+      <c r="K214" t="n">
         <v>0.6750310988820618</v>
       </c>
     </row>
@@ -8607,6 +9251,9 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>19</v>
+      </c>
+      <c r="K215" t="n">
         <v>0.6750310988820618</v>
       </c>
     </row>
@@ -8645,6 +9292,9 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>19</v>
+      </c>
+      <c r="K216" t="n">
         <v>0.549182760801554</v>
       </c>
     </row>
@@ -8683,6 +9333,9 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>19</v>
+      </c>
+      <c r="K217" t="n">
         <v>0.549182760801554</v>
       </c>
     </row>
@@ -8721,6 +9374,9 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>19</v>
+      </c>
+      <c r="K218" t="n">
         <v>0.549182760801554</v>
       </c>
     </row>
@@ -8759,6 +9415,9 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>19</v>
+      </c>
+      <c r="K219" t="n">
         <v>0.549182760801554</v>
       </c>
     </row>
@@ -8797,6 +9456,9 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>19</v>
+      </c>
+      <c r="K220" t="n">
         <v>0.1500163060053583</v>
       </c>
     </row>

--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B03_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_RCA_B03_Normal_2.xlsx
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>34.19156206107118</v>
+        <v>34.1859209565437</v>
       </c>
     </row>
     <row r="4">
@@ -603,7 +603,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>13.70480619480816</v>
+        <v>13.70250628148309</v>
       </c>
     </row>
     <row r="5">
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>13.70480619480816</v>
+        <v>13.70250628148309</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>10.07391314257579</v>
+        <v>10.08259890354299</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>9.086312375561954</v>
+        <v>9.090161634267119</v>
       </c>
     </row>
     <row r="8">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>8.746824124790566</v>
+        <v>8.749064301757452</v>
       </c>
     </row>
     <row r="9">
@@ -808,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>8.218179902291242</v>
+        <v>8.220849820326881</v>
       </c>
     </row>
     <row r="10">
@@ -849,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>7.836770619901664</v>
+        <v>7.837917333184313</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>7.162722102583384</v>
+        <v>7.28780610133979</v>
       </c>
     </row>
     <row r="12">
@@ -931,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>7.310981061882006</v>
+        <v>7.210862258994188</v>
       </c>
     </row>
     <row r="13">
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>7.037492341720552</v>
+        <v>6.939120458610888</v>
       </c>
     </row>
     <row r="14">
@@ -1013,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>7.037492341720552</v>
+        <v>6.939120458610888</v>
       </c>
     </row>
     <row r="15">
@@ -1054,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>6.860158236481039</v>
+        <v>6.857521759342521</v>
       </c>
     </row>
     <row r="16">
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>6.860158236481039</v>
+        <v>6.857521759342521</v>
       </c>
     </row>
     <row r="17">
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>6.860158236481039</v>
+        <v>6.857521759342521</v>
       </c>
     </row>
     <row r="18">
@@ -1177,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>6.462664551863797</v>
+        <v>6.503419128500871</v>
       </c>
     </row>
     <row r="19">
@@ -1218,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>6.336005311670497</v>
+        <v>6.334333511993007</v>
       </c>
     </row>
     <row r="20">
@@ -1259,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>6.336005311670497</v>
+        <v>6.334333511993007</v>
       </c>
     </row>
     <row r="21">
@@ -1300,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>6.336005311670497</v>
+        <v>6.334333511993007</v>
       </c>
     </row>
     <row r="22">
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>6.667695648258961</v>
+        <v>6.6599124093544</v>
       </c>
     </row>
     <row r="23">
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>8.729501710970144</v>
+        <v>8.72269683556639</v>
       </c>
     </row>
     <row r="24">
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>9.435939359634485</v>
+        <v>9.430284900862308</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>11.15912001892901</v>
+        <v>11.15375254245231</v>
       </c>
     </row>
     <row r="26">
@@ -1505,7 +1505,7 @@
         <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>1.227287714443503</v>
+        <v>1.227382935937412</v>
       </c>
     </row>
     <row r="27">
@@ -1546,7 +1546,7 @@
         <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>1.23193593309144</v>
+        <v>1.24106372156266</v>
       </c>
     </row>
     <row r="28">
@@ -1587,7 +1587,7 @@
         <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>1.35533946875624</v>
+        <v>1.354896791708974</v>
       </c>
     </row>
     <row r="29">
@@ -1628,7 +1628,7 @@
         <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>1.35533946875624</v>
+        <v>1.354896791708974</v>
       </c>
     </row>
     <row r="30">
@@ -1669,7 +1669,7 @@
         <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>1.377032682735515</v>
+        <v>1.361693057044747</v>
       </c>
     </row>
     <row r="31">
@@ -1710,7 +1710,7 @@
         <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
     </row>
     <row r="32">
@@ -1751,7 +1751,7 @@
         <v>19</v>
       </c>
       <c r="K32" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
     </row>
     <row r="33">
@@ -1792,7 +1792,7 @@
         <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
     </row>
     <row r="34">
@@ -1833,7 +1833,7 @@
         <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>1.361532670712998</v>
+        <v>1.361693057044747</v>
       </c>
     </row>
     <row r="35">
@@ -1874,7 +1874,7 @@
         <v>19</v>
       </c>
       <c r="K35" t="n">
-        <v>1.332550697377175</v>
+        <v>1.332198337799302</v>
       </c>
     </row>
     <row r="36">
@@ -1915,7 +1915,7 @@
         <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>1.332550697377175</v>
+        <v>1.332198337799302</v>
       </c>
     </row>
     <row r="37">
@@ -1956,7 +1956,7 @@
         <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>1.284651506328684</v>
+        <v>1.284636687860095</v>
       </c>
     </row>
     <row r="38">
@@ -1997,7 +1997,7 @@
         <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>1.107254980884808</v>
+        <v>1.107461427996592</v>
       </c>
     </row>
     <row r="39">
@@ -2038,7 +2038,7 @@
         <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>1.112638311549703</v>
+        <v>1.112797393379885</v>
       </c>
     </row>
     <row r="40">
@@ -2079,7 +2079,7 @@
         <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>1.112638311549703</v>
+        <v>1.112797393379885</v>
       </c>
     </row>
     <row r="41">
@@ -2120,7 +2120,7 @@
         <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>1.257088550825828</v>
+        <v>1.257408492792987</v>
       </c>
     </row>
     <row r="42">
@@ -2161,7 +2161,7 @@
         <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>1.318599484561683</v>
+        <v>1.318824427330396</v>
       </c>
     </row>
     <row r="43">
@@ -2202,7 +2202,7 @@
         <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>1.318599484561683</v>
+        <v>1.318824427330396</v>
       </c>
     </row>
     <row r="44">
@@ -2243,7 +2243,7 @@
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>1.668579154133544</v>
+        <v>1.668702471981479</v>
       </c>
     </row>
     <row r="45">
@@ -2284,7 +2284,7 @@
         <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>2.154789540514063</v>
+        <v>2.153908199193142</v>
       </c>
     </row>
     <row r="46">
@@ -2325,7 +2325,7 @@
         <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>2.297674616284092</v>
+        <v>2.29642073798828</v>
       </c>
     </row>
     <row r="47">
@@ -2366,7 +2366,7 @@
         <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>2.458820606152787</v>
+        <v>2.458253411048135</v>
       </c>
     </row>
     <row r="48">
@@ -2407,7 +2407,7 @@
         <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>2.460406747861397</v>
+        <v>2.460846652165882</v>
       </c>
     </row>
     <row r="49">
@@ -2448,7 +2448,7 @@
         <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>2.410618974223967</v>
+        <v>2.411319919634006</v>
       </c>
     </row>
     <row r="50">
@@ -2489,7 +2489,7 @@
         <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>2.270371957171189</v>
+        <v>2.270446541180712</v>
       </c>
     </row>
     <row r="51">
@@ -2530,7 +2530,7 @@
         <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>2.271869422281108</v>
+        <v>2.272052080753573</v>
       </c>
     </row>
     <row r="52">
@@ -2571,7 +2571,7 @@
         <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>2.271869422281108</v>
+        <v>2.272052080753573</v>
       </c>
     </row>
     <row r="53">
@@ -2612,7 +2612,7 @@
         <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>2.216039524358943</v>
+        <v>2.215926808664032</v>
       </c>
     </row>
     <row r="54">
@@ -2653,7 +2653,7 @@
         <v>19</v>
       </c>
       <c r="K54" t="n">
-        <v>2.216039524358943</v>
+        <v>2.215926808664032</v>
       </c>
     </row>
     <row r="55">
@@ -2694,7 +2694,7 @@
         <v>19</v>
       </c>
       <c r="K55" t="n">
-        <v>2.213941658042832</v>
+        <v>2.21383558243299</v>
       </c>
     </row>
     <row r="56">
@@ -2735,7 +2735,7 @@
         <v>19</v>
       </c>
       <c r="K56" t="n">
-        <v>2.235270250419494</v>
+        <v>2.234827188619676</v>
       </c>
     </row>
     <row r="57">
@@ -2776,7 +2776,7 @@
         <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>2.274306125900985</v>
+        <v>2.27411075658675</v>
       </c>
     </row>
     <row r="58">
@@ -2817,7 +2817,7 @@
         <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>2.274306125900985</v>
+        <v>2.27411075658675</v>
       </c>
     </row>
     <row r="59">
@@ -2858,7 +2858,7 @@
         <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>2.260946222053909</v>
+        <v>2.261921140867016</v>
       </c>
     </row>
     <row r="60">
@@ -2899,7 +2899,7 @@
         <v>19</v>
       </c>
       <c r="K60" t="n">
-        <v>2.183887499719703</v>
+        <v>2.18573777095802</v>
       </c>
     </row>
     <row r="61">
@@ -2940,7 +2940,7 @@
         <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>1.970594865057129</v>
+        <v>1.971921957556851</v>
       </c>
     </row>
     <row r="62">
@@ -2981,7 +2981,7 @@
         <v>19</v>
       </c>
       <c r="K62" t="n">
-        <v>1.910386319788868</v>
+        <v>1.911918446699226</v>
       </c>
     </row>
     <row r="63">
@@ -3022,7 +3022,7 @@
         <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>1.810542151060285</v>
+        <v>1.810672454247252</v>
       </c>
     </row>
     <row r="64">
@@ -3063,7 +3063,7 @@
         <v>19</v>
       </c>
       <c r="K64" t="n">
-        <v>1.829812881081303</v>
+        <v>1.829149160512111</v>
       </c>
     </row>
     <row r="65">
@@ -3104,7 +3104,7 @@
         <v>19</v>
       </c>
       <c r="K65" t="n">
-        <v>1.829812881081303</v>
+        <v>1.829149160512111</v>
       </c>
     </row>
     <row r="66">
@@ -3145,7 +3145,7 @@
         <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>1.991065770279512</v>
+        <v>1.989848067740842</v>
       </c>
     </row>
     <row r="67">
@@ -3186,7 +3186,7 @@
         <v>19</v>
       </c>
       <c r="K67" t="n">
-        <v>1.991065770279512</v>
+        <v>1.989848067740842</v>
       </c>
     </row>
     <row r="68">
@@ -3227,7 +3227,7 @@
         <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>2.137351514017634</v>
+        <v>2.136167422974272</v>
       </c>
     </row>
     <row r="69">
@@ -3268,7 +3268,7 @@
         <v>19</v>
       </c>
       <c r="K69" t="n">
-        <v>2.221422323211839</v>
+        <v>2.221112341003636</v>
       </c>
     </row>
     <row r="70">
@@ -3309,7 +3309,7 @@
         <v>19</v>
       </c>
       <c r="K70" t="n">
-        <v>2.219204132671578</v>
+        <v>2.21950440022878</v>
       </c>
     </row>
     <row r="71">
@@ -3350,7 +3350,7 @@
         <v>19</v>
       </c>
       <c r="K71" t="n">
-        <v>2.215632077142135</v>
+        <v>2.215315479264364</v>
       </c>
     </row>
     <row r="72">
@@ -3391,7 +3391,7 @@
         <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>2.229827140497467</v>
+        <v>2.228902580455803</v>
       </c>
     </row>
     <row r="73">
@@ -3432,7 +3432,7 @@
         <v>19</v>
       </c>
       <c r="K73" t="n">
-        <v>2.229827140497467</v>
+        <v>2.228902580455803</v>
       </c>
     </row>
     <row r="74">
@@ -3473,7 +3473,7 @@
         <v>19</v>
       </c>
       <c r="K74" t="n">
-        <v>2.319870152035572</v>
+        <v>2.31824343275251</v>
       </c>
     </row>
     <row r="75">
@@ -3514,7 +3514,7 @@
         <v>19</v>
       </c>
       <c r="K75" t="n">
-        <v>2.40130937562907</v>
+        <v>2.399449402253348</v>
       </c>
     </row>
     <row r="76">
@@ -3555,7 +3555,7 @@
         <v>19</v>
       </c>
       <c r="K76" t="n">
-        <v>2.40130937562907</v>
+        <v>2.399449402253348</v>
       </c>
     </row>
     <row r="77">
@@ -3596,7 +3596,7 @@
         <v>19</v>
       </c>
       <c r="K77" t="n">
-        <v>2.537929763195659</v>
+        <v>2.53628906525354</v>
       </c>
     </row>
     <row r="78">
@@ -3637,7 +3637,7 @@
         <v>19</v>
       </c>
       <c r="K78" t="n">
-        <v>2.537929763195659</v>
+        <v>2.53628906525354</v>
       </c>
     </row>
     <row r="79">
@@ -3678,7 +3678,7 @@
         <v>19</v>
       </c>
       <c r="K79" t="n">
-        <v>2.568277899878588</v>
+        <v>2.567703330165187</v>
       </c>
     </row>
     <row r="80">
@@ -3719,7 +3719,7 @@
         <v>19</v>
       </c>
       <c r="K80" t="n">
-        <v>2.552397377840622</v>
+        <v>2.553200095302242</v>
       </c>
     </row>
     <row r="81">
@@ -3760,7 +3760,7 @@
         <v>19</v>
       </c>
       <c r="K81" t="n">
-        <v>2.552397377840622</v>
+        <v>2.553200095302242</v>
       </c>
     </row>
     <row r="82">
@@ -3801,7 +3801,7 @@
         <v>19</v>
       </c>
       <c r="K82" t="n">
-        <v>2.52490559672174</v>
+        <v>2.525998643457513</v>
       </c>
     </row>
     <row r="83">
@@ -3842,7 +3842,7 @@
         <v>19</v>
       </c>
       <c r="K83" t="n">
-        <v>2.458664129952975</v>
+        <v>2.460272776605422</v>
       </c>
     </row>
     <row r="84">
@@ -3883,7 +3883,7 @@
         <v>19</v>
       </c>
       <c r="K84" t="n">
-        <v>2.458664129952975</v>
+        <v>2.460272776605422</v>
       </c>
     </row>
     <row r="85">
@@ -3924,7 +3924,7 @@
         <v>19</v>
       </c>
       <c r="K85" t="n">
-        <v>2.340751823293324</v>
+        <v>2.340941256016772</v>
       </c>
     </row>
     <row r="86">
@@ -3965,7 +3965,7 @@
         <v>19</v>
       </c>
       <c r="K86" t="n">
-        <v>2.336561586544111</v>
+        <v>2.336857632616919</v>
       </c>
     </row>
     <row r="87">
@@ -4006,7 +4006,7 @@
         <v>19</v>
       </c>
       <c r="K87" t="n">
-        <v>2.328929626762258</v>
+        <v>2.32909000814458</v>
       </c>
     </row>
     <row r="88">
@@ -4047,7 +4047,7 @@
         <v>19</v>
       </c>
       <c r="K88" t="n">
-        <v>2.291460197292751</v>
+        <v>2.292277987951941</v>
       </c>
     </row>
     <row r="89">
@@ -4088,7 +4088,7 @@
         <v>19</v>
       </c>
       <c r="K89" t="n">
-        <v>2.291460197292751</v>
+        <v>2.292277987951941</v>
       </c>
     </row>
     <row r="90">
@@ -4129,7 +4129,7 @@
         <v>19</v>
       </c>
       <c r="K90" t="n">
-        <v>2.291460197292751</v>
+        <v>2.292277987951941</v>
       </c>
     </row>
     <row r="91">
@@ -4170,7 +4170,7 @@
         <v>19</v>
       </c>
       <c r="K91" t="n">
-        <v>2.256392889218995</v>
+        <v>2.256972399806862</v>
       </c>
     </row>
     <row r="92">
@@ -4211,7 +4211,7 @@
         <v>19</v>
       </c>
       <c r="K92" t="n">
-        <v>2.252810073838055</v>
+        <v>2.253288682135747</v>
       </c>
     </row>
     <row r="93">
@@ -4252,7 +4252,7 @@
         <v>19</v>
       </c>
       <c r="K93" t="n">
-        <v>2.252810073838055</v>
+        <v>2.253288682135747</v>
       </c>
     </row>
     <row r="94">
@@ -4293,7 +4293,7 @@
         <v>19</v>
       </c>
       <c r="K94" t="n">
-        <v>2.241589356169574</v>
+        <v>2.241708558609957</v>
       </c>
     </row>
     <row r="95">
@@ -4334,7 +4334,7 @@
         <v>19</v>
       </c>
       <c r="K95" t="n">
-        <v>2.256258194428659</v>
+        <v>2.255753292983399</v>
       </c>
     </row>
     <row r="96">
@@ -4375,7 +4375,7 @@
         <v>19</v>
       </c>
       <c r="K96" t="n">
-        <v>2.275320402532291</v>
+        <v>2.274494923648692</v>
       </c>
     </row>
     <row r="97">
@@ -4416,7 +4416,7 @@
         <v>19</v>
       </c>
       <c r="K97" t="n">
-        <v>2.275320402532291</v>
+        <v>2.302930674306835</v>
       </c>
     </row>
     <row r="98">
@@ -4457,7 +4457,7 @@
         <v>19</v>
       </c>
       <c r="K98" t="n">
-        <v>2.34160528784422</v>
+        <v>2.33992287022176</v>
       </c>
     </row>
     <row r="99">
@@ -4498,7 +4498,7 @@
         <v>19</v>
       </c>
       <c r="K99" t="n">
-        <v>2.34160528784422</v>
+        <v>2.33992287022176</v>
       </c>
     </row>
     <row r="100">
@@ -4539,7 +4539,7 @@
         <v>19</v>
       </c>
       <c r="K100" t="n">
-        <v>2.530274206826251</v>
+        <v>2.528368514819499</v>
       </c>
     </row>
     <row r="101">
@@ -4580,7 +4580,7 @@
         <v>19</v>
       </c>
       <c r="K101" t="n">
-        <v>2.530274206826251</v>
+        <v>2.528368514819499</v>
       </c>
     </row>
     <row r="102">
@@ -4621,7 +4621,7 @@
         <v>19</v>
       </c>
       <c r="K102" t="n">
-        <v>2.584584463834299</v>
+        <v>2.584006862581848</v>
       </c>
     </row>
     <row r="103">
@@ -4662,7 +4662,7 @@
         <v>19</v>
       </c>
       <c r="K103" t="n">
-        <v>2.586206055763945</v>
+        <v>2.586709133287388</v>
       </c>
     </row>
     <row r="104">
@@ -4703,7 +4703,7 @@
         <v>19</v>
       </c>
       <c r="K104" t="n">
-        <v>2.586206055763945</v>
+        <v>2.586709133287388</v>
       </c>
     </row>
     <row r="105">
@@ -4744,7 +4744,7 @@
         <v>19</v>
       </c>
       <c r="K105" t="n">
-        <v>2.586206055763945</v>
+        <v>2.586709133287388</v>
       </c>
     </row>
     <row r="106">
@@ -4785,7 +4785,7 @@
         <v>19</v>
       </c>
       <c r="K106" t="n">
-        <v>2.544664688156764</v>
+        <v>2.54484718829641</v>
       </c>
     </row>
     <row r="107">
@@ -4826,7 +4826,7 @@
         <v>19</v>
       </c>
       <c r="K107" t="n">
-        <v>2.529506928743095</v>
+        <v>2.530712990426041</v>
       </c>
     </row>
     <row r="108">
@@ -4867,7 +4867,7 @@
         <v>19</v>
       </c>
       <c r="K108" t="n">
-        <v>2.497336168150439</v>
+        <v>2.500363114220298</v>
       </c>
     </row>
     <row r="109">
@@ -4908,7 +4908,7 @@
         <v>19</v>
       </c>
       <c r="K109" t="n">
-        <v>2.446076643315274</v>
+        <v>2.451535302424364</v>
       </c>
     </row>
     <row r="110">
@@ -4949,7 +4949,7 @@
         <v>19</v>
       </c>
       <c r="K110" t="n">
-        <v>2.411004224014718</v>
+        <v>2.411460941051728</v>
       </c>
     </row>
     <row r="111">
@@ -4990,7 +4990,7 @@
         <v>19</v>
       </c>
       <c r="K111" t="n">
-        <v>2.401508938888195</v>
+        <v>2.390129634984446</v>
       </c>
     </row>
     <row r="112">
@@ -5031,7 +5031,7 @@
         <v>19</v>
       </c>
       <c r="K112" t="n">
-        <v>2.401508938888195</v>
+        <v>2.390129634984446</v>
       </c>
     </row>
     <row r="113">
@@ -5072,7 +5072,7 @@
         <v>19</v>
       </c>
       <c r="K113" t="n">
-        <v>2.355374210797699</v>
+        <v>2.339746983234845</v>
       </c>
     </row>
     <row r="114">
@@ -5113,7 +5113,7 @@
         <v>19</v>
       </c>
       <c r="K114" t="n">
-        <v>2.355374210797699</v>
+        <v>2.339746983234845</v>
       </c>
     </row>
     <row r="115">
@@ -5154,7 +5154,7 @@
         <v>19</v>
       </c>
       <c r="K115" t="n">
-        <v>2.315226465388985</v>
+        <v>2.311422362296051</v>
       </c>
     </row>
     <row r="116">
@@ -5195,7 +5195,7 @@
         <v>19</v>
       </c>
       <c r="K116" t="n">
-        <v>2.315226465388985</v>
+        <v>2.311422362296051</v>
       </c>
     </row>
     <row r="117">
@@ -5236,7 +5236,7 @@
         <v>19</v>
       </c>
       <c r="K117" t="n">
-        <v>2.457069773380443</v>
+        <v>2.45584612763724</v>
       </c>
     </row>
     <row r="118">
@@ -5277,7 +5277,7 @@
         <v>19</v>
       </c>
       <c r="K118" t="n">
-        <v>2.457069773380443</v>
+        <v>2.45584612763724</v>
       </c>
     </row>
     <row r="119">
@@ -5318,7 +5318,7 @@
         <v>19</v>
       </c>
       <c r="K119" t="n">
-        <v>2.482427983219213</v>
+        <v>2.482296945838069</v>
       </c>
     </row>
     <row r="120">
@@ -5359,7 +5359,7 @@
         <v>19</v>
       </c>
       <c r="K120" t="n">
-        <v>2.511628680011507</v>
+        <v>2.510379246784962</v>
       </c>
     </row>
     <row r="121">
@@ -5400,7 +5400,7 @@
         <v>19</v>
       </c>
       <c r="K121" t="n">
-        <v>2.552545134477885</v>
+        <v>2.552119591261148</v>
       </c>
     </row>
     <row r="122">
@@ -5441,7 +5441,7 @@
         <v>19</v>
       </c>
       <c r="K122" t="n">
-        <v>2.555830182603009</v>
+        <v>2.555912126937463</v>
       </c>
     </row>
     <row r="123">
@@ -5482,7 +5482,7 @@
         <v>19</v>
       </c>
       <c r="K123" t="n">
-        <v>2.549148888523415</v>
+        <v>2.54962759680487</v>
       </c>
     </row>
     <row r="124">
@@ -5523,7 +5523,7 @@
         <v>19</v>
       </c>
       <c r="K124" t="n">
-        <v>2.515759755719835</v>
+        <v>2.515616111885459</v>
       </c>
     </row>
     <row r="125">
@@ -5564,7 +5564,7 @@
         <v>19</v>
       </c>
       <c r="K125" t="n">
-        <v>2.528679156446047</v>
+        <v>2.52834745651818</v>
       </c>
     </row>
     <row r="126">
@@ -5605,7 +5605,7 @@
         <v>19</v>
       </c>
       <c r="K126" t="n">
-        <v>2.533869015876358</v>
+        <v>2.533854113018922</v>
       </c>
     </row>
     <row r="127">
@@ -5646,7 +5646,7 @@
         <v>19</v>
       </c>
       <c r="K127" t="n">
-        <v>2.530864023077452</v>
+        <v>2.531204737504585</v>
       </c>
     </row>
     <row r="128">
@@ -5687,7 +5687,7 @@
         <v>19</v>
       </c>
       <c r="K128" t="n">
-        <v>2.516545216993899</v>
+        <v>2.516485706149343</v>
       </c>
     </row>
     <row r="129">
@@ -5728,7 +5728,7 @@
         <v>19</v>
       </c>
       <c r="K129" t="n">
-        <v>2.516545216993899</v>
+        <v>2.516485706149343</v>
       </c>
     </row>
     <row r="130">
@@ -5769,7 +5769,7 @@
         <v>19</v>
       </c>
       <c r="K130" t="n">
-        <v>2.516545216993899</v>
+        <v>2.52260041570954</v>
       </c>
     </row>
     <row r="131">
@@ -5810,7 +5810,7 @@
         <v>19</v>
       </c>
       <c r="K131" t="n">
-        <v>2.523017728759505</v>
+        <v>2.52260041570954</v>
       </c>
     </row>
     <row r="132">
@@ -5851,7 +5851,7 @@
         <v>19</v>
       </c>
       <c r="K132" t="n">
-        <v>2.543958390346354</v>
+        <v>2.543868584742552</v>
       </c>
     </row>
     <row r="133">
@@ -5892,7 +5892,7 @@
         <v>19</v>
       </c>
       <c r="K133" t="n">
-        <v>2.543958390346354</v>
+        <v>2.543868584742552</v>
       </c>
     </row>
     <row r="134">
@@ -5933,7 +5933,7 @@
         <v>19</v>
       </c>
       <c r="K134" t="n">
-        <v>2.485677645008055</v>
+        <v>2.486985759527316</v>
       </c>
     </row>
     <row r="135">
@@ -5974,7 +5974,7 @@
         <v>19</v>
       </c>
       <c r="K135" t="n">
-        <v>2.485677645008055</v>
+        <v>2.453235713426281</v>
       </c>
     </row>
     <row r="136">
@@ -6015,7 +6015,7 @@
         <v>19</v>
       </c>
       <c r="K136" t="n">
-        <v>2.451207524165408</v>
+        <v>2.453235713426281</v>
       </c>
     </row>
     <row r="137">
@@ -6056,7 +6056,7 @@
         <v>19</v>
       </c>
       <c r="K137" t="n">
-        <v>2.402168259650153</v>
+        <v>2.40495911174157</v>
       </c>
     </row>
     <row r="138">
@@ -6097,7 +6097,7 @@
         <v>19</v>
       </c>
       <c r="K138" t="n">
-        <v>2.402168259650153</v>
+        <v>2.40495911174157</v>
       </c>
     </row>
     <row r="139">
@@ -6138,7 +6138,7 @@
         <v>19</v>
       </c>
       <c r="K139" t="n">
-        <v>2.190765346481614</v>
+        <v>2.194344862432881</v>
       </c>
     </row>
     <row r="140">
@@ -6179,7 +6179,7 @@
         <v>19</v>
       </c>
       <c r="K140" t="n">
-        <v>2.123036630767556</v>
+        <v>2.127609197394967</v>
       </c>
     </row>
     <row r="141">
@@ -6220,7 +6220,7 @@
         <v>19</v>
       </c>
       <c r="K141" t="n">
-        <v>2.019402621132054</v>
+        <v>2.020965165643478</v>
       </c>
     </row>
     <row r="142">
@@ -6261,7 +6261,7 @@
         <v>19</v>
       </c>
       <c r="K142" t="n">
-        <v>1.992580752593158</v>
+        <v>1.992690625306859</v>
       </c>
     </row>
     <row r="143">
@@ -6302,7 +6302,7 @@
         <v>19</v>
       </c>
       <c r="K143" t="n">
-        <v>1.992580752593158</v>
+        <v>1.992690625306859</v>
       </c>
     </row>
     <row r="144">
@@ -6343,7 +6343,7 @@
         <v>19</v>
       </c>
       <c r="K144" t="n">
-        <v>1.957100819987285</v>
+        <v>1.95763951878183</v>
       </c>
     </row>
     <row r="145">
@@ -6384,7 +6384,7 @@
         <v>19</v>
       </c>
       <c r="K145" t="n">
-        <v>1.912286907795664</v>
+        <v>1.91398474405841</v>
       </c>
     </row>
     <row r="146">
@@ -6425,7 +6425,7 @@
         <v>19</v>
       </c>
       <c r="K146" t="n">
-        <v>1.880302071203517</v>
+        <v>1.880763567036991</v>
       </c>
     </row>
     <row r="147">
@@ -6466,7 +6466,7 @@
         <v>19</v>
       </c>
       <c r="K147" t="n">
-        <v>1.833191292616835</v>
+        <v>1.833305263923982</v>
       </c>
     </row>
     <row r="148">
@@ -6507,7 +6507,7 @@
         <v>19</v>
       </c>
       <c r="K148" t="n">
-        <v>1.835108269023008</v>
+        <v>1.835471097545149</v>
       </c>
     </row>
     <row r="149">
@@ -6548,7 +6548,7 @@
         <v>19</v>
       </c>
       <c r="K149" t="n">
-        <v>1.837290468265474</v>
+        <v>1.838170620522636</v>
       </c>
     </row>
     <row r="150">
@@ -6589,7 +6589,7 @@
         <v>19</v>
       </c>
       <c r="K150" t="n">
-        <v>1.851183425352798</v>
+        <v>1.852734478318536</v>
       </c>
     </row>
     <row r="151">
@@ -6630,7 +6630,7 @@
         <v>19</v>
       </c>
       <c r="K151" t="n">
-        <v>1.851183425352798</v>
+        <v>1.852734478318536</v>
       </c>
     </row>
     <row r="152">
@@ -6671,7 +6671,7 @@
         <v>19</v>
       </c>
       <c r="K152" t="n">
-        <v>1.851183425352798</v>
+        <v>1.852734478318536</v>
       </c>
     </row>
     <row r="153">
@@ -6712,7 +6712,7 @@
         <v>19</v>
       </c>
       <c r="K153" t="n">
-        <v>1.918307120376766</v>
+        <v>1.914609353839869</v>
       </c>
     </row>
     <row r="154">
@@ -6753,7 +6753,7 @@
         <v>19</v>
       </c>
       <c r="K154" t="n">
-        <v>1.985832791947801</v>
+        <v>1.986039459425867</v>
       </c>
     </row>
     <row r="155">
@@ -6794,7 +6794,7 @@
         <v>19</v>
       </c>
       <c r="K155" t="n">
-        <v>1.94111181613984</v>
+        <v>1.943612908866282</v>
       </c>
     </row>
     <row r="156">
@@ -6835,7 +6835,7 @@
         <v>19</v>
       </c>
       <c r="K156" t="n">
-        <v>1.884597235153793</v>
+        <v>1.88775516460374</v>
       </c>
     </row>
     <row r="157">
@@ -6876,7 +6876,7 @@
         <v>19</v>
       </c>
       <c r="K157" t="n">
-        <v>1.884597235153793</v>
+        <v>1.88775516460374</v>
       </c>
     </row>
     <row r="158">
@@ -6917,7 +6917,7 @@
         <v>19</v>
       </c>
       <c r="K158" t="n">
-        <v>1.884597235153793</v>
+        <v>1.809336938530754</v>
       </c>
     </row>
     <row r="159">
@@ -6958,7 +6958,7 @@
         <v>19</v>
       </c>
       <c r="K159" t="n">
-        <v>1.621958698060077</v>
+        <v>1.62660465915978</v>
       </c>
     </row>
     <row r="160">
@@ -6999,7 +6999,7 @@
         <v>19</v>
       </c>
       <c r="K160" t="n">
-        <v>1.621958698060077</v>
+        <v>1.62660465915978</v>
       </c>
     </row>
     <row r="161">
@@ -7040,7 +7040,7 @@
         <v>19</v>
       </c>
       <c r="K161" t="n">
-        <v>1.379798047976322</v>
+        <v>1.382072456968563</v>
       </c>
     </row>
     <row r="162">
@@ -7081,7 +7081,7 @@
         <v>19</v>
       </c>
       <c r="K162" t="n">
-        <v>1.333362209138855</v>
+        <v>1.33559316674232</v>
       </c>
     </row>
     <row r="163">
@@ -7122,7 +7122,7 @@
         <v>19</v>
       </c>
       <c r="K163" t="n">
-        <v>1.333362209138855</v>
+        <v>1.289724165900363</v>
       </c>
     </row>
     <row r="164">
@@ -7163,7 +7163,7 @@
         <v>19</v>
       </c>
       <c r="K164" t="n">
-        <v>1.287433504266253</v>
+        <v>1.289724165900363</v>
       </c>
     </row>
     <row r="165">
@@ -7204,7 +7204,7 @@
         <v>19</v>
       </c>
       <c r="K165" t="n">
-        <v>1.211808301441334</v>
+        <v>1.212551325507892</v>
       </c>
     </row>
     <row r="166">
@@ -7245,7 +7245,7 @@
         <v>19</v>
       </c>
       <c r="K166" t="n">
-        <v>1.205523507937499</v>
+        <v>1.206739525023695</v>
       </c>
     </row>
     <row r="167">
@@ -7286,7 +7286,7 @@
         <v>19</v>
       </c>
       <c r="K167" t="n">
-        <v>1.205523507937499</v>
+        <v>1.206739525023695</v>
       </c>
     </row>
     <row r="168">
@@ -7327,7 +7327,7 @@
         <v>19</v>
       </c>
       <c r="K168" t="n">
-        <v>1.205523507937499</v>
+        <v>1.206739525023695</v>
       </c>
     </row>
     <row r="169">
@@ -7368,7 +7368,7 @@
         <v>19</v>
       </c>
       <c r="K169" t="n">
-        <v>1.1928574441495</v>
+        <v>1.192412560549965</v>
       </c>
     </row>
     <row r="170">
@@ -7409,7 +7409,7 @@
         <v>19</v>
       </c>
       <c r="K170" t="n">
-        <v>1.16536180842725</v>
+        <v>1.165322041777845</v>
       </c>
     </row>
     <row r="171">
@@ -7450,7 +7450,7 @@
         <v>19</v>
       </c>
       <c r="K171" t="n">
-        <v>1.16536180842725</v>
+        <v>1.165322041777845</v>
       </c>
     </row>
     <row r="172">
@@ -7491,7 +7491,7 @@
         <v>19</v>
       </c>
       <c r="K172" t="n">
-        <v>1.236228494084955</v>
+        <v>1.234632837280565</v>
       </c>
     </row>
     <row r="173">
@@ -7532,7 +7532,7 @@
         <v>19</v>
       </c>
       <c r="K173" t="n">
-        <v>1.236228494084955</v>
+        <v>1.234632837280565</v>
       </c>
     </row>
     <row r="174">
@@ -7573,7 +7573,7 @@
         <v>19</v>
       </c>
       <c r="K174" t="n">
-        <v>1.260336599441735</v>
+        <v>1.259479778907701</v>
       </c>
     </row>
     <row r="175">
@@ -7614,7 +7614,7 @@
         <v>19</v>
       </c>
       <c r="K175" t="n">
-        <v>1.297429051340093</v>
+        <v>1.297041515423841</v>
       </c>
     </row>
     <row r="176">
@@ -7655,7 +7655,7 @@
         <v>19</v>
       </c>
       <c r="K176" t="n">
-        <v>1.297429051340093</v>
+        <v>1.297041515423841</v>
       </c>
     </row>
     <row r="177">
@@ -7696,7 +7696,7 @@
         <v>19</v>
       </c>
       <c r="K177" t="n">
-        <v>1.30326712508255</v>
+        <v>1.30334220224594</v>
       </c>
     </row>
     <row r="178">
@@ -7737,7 +7737,7 @@
         <v>19</v>
       </c>
       <c r="K178" t="n">
-        <v>1.281377167733944</v>
+        <v>1.283448220578055</v>
       </c>
     </row>
     <row r="179">
@@ -7778,7 +7778,7 @@
         <v>19</v>
       </c>
       <c r="K179" t="n">
-        <v>1.251783703030703</v>
+        <v>1.254499829613582</v>
       </c>
     </row>
     <row r="180">
@@ -7819,7 +7819,7 @@
         <v>19</v>
       </c>
       <c r="K180" t="n">
-        <v>1.227335525810869</v>
+        <v>1.224959555379384</v>
       </c>
     </row>
     <row r="181">
@@ -7860,7 +7860,7 @@
         <v>19</v>
       </c>
       <c r="K181" t="n">
-        <v>1.243950820717568</v>
+        <v>1.241736362431915</v>
       </c>
     </row>
     <row r="182">
@@ -7901,7 +7901,7 @@
         <v>19</v>
       </c>
       <c r="K182" t="n">
-        <v>1.243950820717568</v>
+        <v>1.241736362431915</v>
       </c>
     </row>
     <row r="183">
@@ -7942,7 +7942,7 @@
         <v>19</v>
       </c>
       <c r="K183" t="n">
-        <v>1.243950820717568</v>
+        <v>1.241736362431915</v>
       </c>
     </row>
     <row r="184">
@@ -7983,7 +7983,7 @@
         <v>19</v>
       </c>
       <c r="K184" t="n">
-        <v>1.289010081981549</v>
+        <v>1.289442800577439</v>
       </c>
     </row>
     <row r="185">
@@ -8024,7 +8024,7 @@
         <v>19</v>
       </c>
       <c r="K185" t="n">
-        <v>1.289010081981549</v>
+        <v>1.289442800577439</v>
       </c>
     </row>
     <row r="186">
@@ -8065,7 +8065,7 @@
         <v>19</v>
       </c>
       <c r="K186" t="n">
-        <v>1.30978613598686</v>
+        <v>1.31326574375713</v>
       </c>
     </row>
     <row r="187">
@@ -8106,7 +8106,7 @@
         <v>19</v>
       </c>
       <c r="K187" t="n">
-        <v>1.30978613598686</v>
+        <v>1.359042505236806</v>
       </c>
     </row>
     <row r="188">
@@ -8147,7 +8147,7 @@
         <v>19</v>
       </c>
       <c r="K188" t="n">
-        <v>1.353093274823836</v>
+        <v>1.359042505236806</v>
       </c>
     </row>
     <row r="189">
@@ -8188,7 +8188,7 @@
         <v>19</v>
       </c>
       <c r="K189" t="n">
-        <v>1.349097862080286</v>
+        <v>1.351998829157492</v>
       </c>
     </row>
     <row r="190">
@@ -8229,7 +8229,7 @@
         <v>19</v>
       </c>
       <c r="K190" t="n">
-        <v>1.349097862080286</v>
+        <v>1.351998829157492</v>
       </c>
     </row>
     <row r="191">
@@ -8270,7 +8270,7 @@
         <v>19</v>
       </c>
       <c r="K191" t="n">
-        <v>1.349097862080286</v>
+        <v>1.351998829157492</v>
       </c>
     </row>
     <row r="192">
@@ -8311,7 +8311,7 @@
         <v>19</v>
       </c>
       <c r="K192" t="n">
-        <v>1.249019127836197</v>
+        <v>1.252221301150578</v>
       </c>
     </row>
     <row r="193">
@@ -8352,7 +8352,7 @@
         <v>19</v>
       </c>
       <c r="K193" t="n">
-        <v>1.146242541840859</v>
+        <v>1.151677425181881</v>
       </c>
     </row>
     <row r="194">
@@ -8393,7 +8393,7 @@
         <v>19</v>
       </c>
       <c r="K194" t="n">
-        <v>1.071318962206051</v>
+        <v>1.074753893044807</v>
       </c>
     </row>
     <row r="195">
@@ -8434,7 +8434,7 @@
         <v>19</v>
       </c>
       <c r="K195" t="n">
-        <v>0.9282874515275316</v>
+        <v>0.9293217077643242</v>
       </c>
     </row>
     <row r="196">
@@ -8475,7 +8475,7 @@
         <v>19</v>
       </c>
       <c r="K196" t="n">
-        <v>0.8844761571323866</v>
+        <v>0.8843090081545558</v>
       </c>
     </row>
     <row r="197">
@@ -8516,7 +8516,7 @@
         <v>19</v>
       </c>
       <c r="K197" t="n">
-        <v>0.8922070873695911</v>
+        <v>0.8918796143983428</v>
       </c>
     </row>
     <row r="198">
@@ -8557,7 +8557,7 @@
         <v>19</v>
       </c>
       <c r="K198" t="n">
-        <v>1.145696371936362</v>
+        <v>1.143035239705504</v>
       </c>
     </row>
     <row r="199">
@@ -8598,7 +8598,7 @@
         <v>19</v>
       </c>
       <c r="K199" t="n">
-        <v>1.210838832206954</v>
+        <v>1.208876145314666</v>
       </c>
     </row>
     <row r="200">
@@ -8639,7 +8639,7 @@
         <v>19</v>
       </c>
       <c r="K200" t="n">
-        <v>1.265759784093344</v>
+        <v>1.265348069603777</v>
       </c>
     </row>
     <row r="201">
@@ -8680,7 +8680,7 @@
         <v>19</v>
       </c>
       <c r="K201" t="n">
-        <v>1.265759784093344</v>
+        <v>1.265348069603777</v>
       </c>
     </row>
     <row r="202">
@@ -8721,7 +8721,7 @@
         <v>19</v>
       </c>
       <c r="K202" t="n">
-        <v>1.296048767498403</v>
+        <v>1.298981901047366</v>
       </c>
     </row>
     <row r="203">
@@ -8762,7 +8762,7 @@
         <v>19</v>
       </c>
       <c r="K203" t="n">
-        <v>1.298801741278553</v>
+        <v>1.298981901047366</v>
       </c>
     </row>
     <row r="204">
@@ -8803,7 +8803,7 @@
         <v>19</v>
       </c>
       <c r="K204" t="n">
-        <v>1.286869092677173</v>
+        <v>1.287600716901656</v>
       </c>
     </row>
     <row r="205">
@@ -8844,7 +8844,7 @@
         <v>19</v>
       </c>
       <c r="K205" t="n">
-        <v>1.233372560532288</v>
+        <v>1.234526023781353</v>
       </c>
     </row>
     <row r="206">
@@ -8885,7 +8885,7 @@
         <v>19</v>
       </c>
       <c r="K206" t="n">
-        <v>1.233372560532288</v>
+        <v>1.234526023781353</v>
       </c>
     </row>
     <row r="207">
@@ -8926,7 +8926,7 @@
         <v>19</v>
       </c>
       <c r="K207" t="n">
-        <v>1.13176711732786</v>
+        <v>1.135750742934406</v>
       </c>
     </row>
     <row r="208">
@@ -8967,7 +8967,7 @@
         <v>19</v>
       </c>
       <c r="K208" t="n">
-        <v>0.936908567612344</v>
+        <v>0.9438187947621866</v>
       </c>
     </row>
     <row r="209">
@@ -9008,7 +9008,7 @@
         <v>19</v>
       </c>
       <c r="K209" t="n">
-        <v>0.8539973695115169</v>
+        <v>0.8586149336110689</v>
       </c>
     </row>
     <row r="210">
@@ -9049,7 +9049,7 @@
         <v>19</v>
       </c>
       <c r="K210" t="n">
-        <v>0.822075033593868</v>
+        <v>0.82347174497717</v>
       </c>
     </row>
     <row r="211">
@@ -9090,7 +9090,7 @@
         <v>19</v>
       </c>
       <c r="K211" t="n">
-        <v>0.822075033593868</v>
+        <v>0.82347174497717</v>
       </c>
     </row>
     <row r="212">
@@ -9131,7 +9131,7 @@
         <v>19</v>
       </c>
       <c r="K212" t="n">
-        <v>0.7864108338360511</v>
+        <v>0.7391853344810749</v>
       </c>
     </row>
     <row r="213">
@@ -9172,7 +9172,7 @@
         <v>19</v>
       </c>
       <c r="K213" t="n">
-        <v>0.7371944434193791</v>
+        <v>0.7391853344810749</v>
       </c>
     </row>
     <row r="214">
@@ -9213,7 +9213,7 @@
         <v>19</v>
       </c>
       <c r="K214" t="n">
-        <v>0.6750310988820618</v>
+        <v>0.678101286899057</v>
       </c>
     </row>
     <row r="215">
@@ -9254,7 +9254,7 @@
         <v>19</v>
       </c>
       <c r="K215" t="n">
-        <v>0.6750310988820618</v>
+        <v>0.678101286899057</v>
       </c>
     </row>
     <row r="216">
@@ -9295,7 +9295,7 @@
         <v>19</v>
       </c>
       <c r="K216" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
     </row>
     <row r="217">
@@ -9336,7 +9336,7 @@
         <v>19</v>
       </c>
       <c r="K217" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
     </row>
     <row r="218">
@@ -9377,7 +9377,7 @@
         <v>19</v>
       </c>
       <c r="K218" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
     </row>
     <row r="219">
@@ -9418,7 +9418,7 @@
         <v>19</v>
       </c>
       <c r="K219" t="n">
-        <v>0.549182760801554</v>
+        <v>0.5523719819007573</v>
       </c>
     </row>
     <row r="220">
@@ -9459,7 +9459,7 @@
         <v>19</v>
       </c>
       <c r="K220" t="n">
-        <v>0.1500163060053583</v>
+        <v>0.155202974904865</v>
       </c>
     </row>
   </sheetData>
